--- a/DOSSIES_MULTIFORMATO/SEFAZ/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEFAZ/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025NE0000095</t>
+          <t>2025NE0000096</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>583.89</v>
+        <v>1110.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -659,14 +659,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Contratação para fornecimento de licença de uso, compreendendo a disponibilização de Plataforma de Comunicação e Colaboração em plataforma Web – APLICAÇÃO POWER BI. TC: 0032/2024 AD: 01.</t>
+          <t>Contratação para fornecimento de licença de uso, compreendendo a disponibilização de Plataforma de Comunicação e Colaboração em plataforma Web – APLICAÇÃO POWER BI.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025NE0000096</t>
+          <t>2025NE0000095</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1110.8</v>
+        <v>583.89</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Contratação para fornecimento de licença de uso, compreendendo a disponibilização de Plataforma de Comunicação e Colaboração em plataforma Web – APLICAÇÃO POWER BI.</t>
+          <t>Contratação para fornecimento de licença de uso, compreendendo a disponibilização de Plataforma de Comunicação e Colaboração em plataforma Web – APLICAÇÃO POWER BI. TC: 0032/2024 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2016NE01699</t>
+          <t>2016NE01697</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96598.67</v>
+        <v>636597.39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2016NE01698</t>
+          <t>2016NE01696</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>318705.8</v>
+        <v>182951.22</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2016NE01696</t>
+          <t>2016NE01698</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>182951.22</v>
+        <v>318705.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2016NE01697</t>
+          <t>2016NE01699</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>636597.39</v>
+        <v>96598.67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -878,21 +878,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2016NE01502</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2016NE01501</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>30/11/2016</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>98660.50999999999</v>
+        <v>1339.49</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -908,17 +904,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2016NE01501</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>2016NE01502</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>30/11/2016</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1339.49</v>
+        <v>98660.50999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2017NE01250</t>
+          <t>2017NE01251</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1711203.6</v>
+        <v>297176.23</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anulação do saldo da 2017NE00031.</t>
+          <t>Anulação do saldo da 2017NE00317.</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2017NE01251</t>
+          <t>2017NE01250</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>297176.23</v>
+        <v>1711203.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anulação do saldo da 2017NE00317.</t>
+          <t>Anulação do saldo da 2017NE00031.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2018NE01281</t>
+          <t>2018NE01282</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>114367.9</v>
+        <v>94978.78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE01282</t>
+          <t>2018NE01281</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>94978.78</v>
+        <v>114367.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017NE00071</t>
+          <t>2017NE01435</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.83</v>
+        <v>58.61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017NE01435</t>
+          <t>2017NE00071</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>58.61</v>
+        <v>1.83</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1620,21 +1620,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018NE00579</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2018NE00584</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>25/05/2018</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>591968.04</v>
+        <v>271717.92</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1643,24 +1639,28 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
+          <t>Convênio Nº 05/2015-PRODAM, de forma a contemplar a concessão de gratificação de representação e reenquadramento dos técnicos cedidos para atuarem na área de Tecnologia da Informação da SEFAZ, conform</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018NE00584</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>2018NE00579</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>25/05/2018</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>271717.92</v>
+        <v>591968.04</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Convênio Nº 05/2015-PRODAM, de forma a contemplar a concessão de gratificação de representação e reenquadramento dos técnicos cedidos para atuarem na área de Tecnologia da Informação da SEFAZ, conform</t>
+          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2019NE00394</t>
+          <t>2019NE00406</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cancelamento devido a equivoco no numero do processo</t>
+          <t>Despesa referente à cessão, por disposição, da PRODAM - Processamento de Dados do Amazonas S.A., de técnicos constantes em anexo ao documento DIRAF/199 de 25/09/2018.</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2019NE00406</t>
+          <t>2019NE00394</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Despesa referente à cessão, por disposição, da PRODAM - Processamento de Dados do Amazonas S.A., de técnicos constantes em anexo ao documento DIRAF/199 de 25/09/2018.</t>
+          <t>Cancelamento devido a equivoco no numero do processo</t>
         </is>
       </c>
     </row>
@@ -1810,10 +1810,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2017NE00807</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>2017NE00808</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>24/07/2017</t>
@@ -1829,7 +1833,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cancelamento por equivoco na modalidade</t>
+          <t>Prorrogação do prazo de vigência e supressão, referente a prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
         </is>
       </c>
     </row>
@@ -1866,14 +1870,10 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2017NE00808</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2017NE00807</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>24/07/2017</t>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Prorrogação do prazo de vigência e supressão, referente a prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
+          <t>Cancelamento por equivoco na modalidade</t>
         </is>
       </c>
     </row>
@@ -2198,10 +2198,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2019NE00663</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>2019NE00661</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>21/06/2019</t>
@@ -2217,21 +2221,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anulação Total da NE acima descrita devido equivoco na data de emissão.</t>
+          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2019NE00661</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2019NE00663</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>21/06/2019</t>
@@ -2247,21 +2247,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
+          <t>Anulação Total da NE acima descrita devido equivoco na data de emissão.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2021NE0000005</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>12/2023</t>
-        </is>
-      </c>
+          <t>2021NE0000001</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>21/01/2021</t>
@@ -2277,17 +2273,21 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anulação total do empenho por erro na data de emissão.</t>
+          <t>Cessão de servidores da PRODAM para prestar serviços na SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2021NE0000001</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>2021NE0000005</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12/2023</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>21/01/2021</t>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cessão de servidores da PRODAM para prestar serviços na SEFAZ.</t>
+          <t>Anulação total do empenho por erro na data de emissão.</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2015NE00249</t>
+          <t>2015NE00256</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10/2009</t>
+          <t>1/2010</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>31835.61</v>
+        <v>257473.08</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2699,19 +2699,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestação de serviços especializados em informática em geral. Serviços de hospedagem com infraestrutura para armazenamento do Sistema de Controle de Material e Patrimônio ¿ AJURI, referente ao mês de </t>
+          <t>Prestação de serviços técnicos especializados na área de tecnologia da infformação - TI, referente ao mês de novembro/2014, relativo ao Contrato nº 001/2010.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2015NE00250</t>
+          <t>2015NE00255</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10/2009</t>
+          <t>1/2010</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>31835.61</v>
+        <v>257473.08</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestação de serviços especializados em informática em geral. Serviços de hospedagem com infraestrutura para armazenamento do Sistema de Controle de Material e Patrimônio ¿ AJURI, referente ao mês de </t>
+          <t>CANCELAMENTO DA NE ACIMA DESCRITA DEVIDO A EQUÍVOCO NA FONTE DE RECURSO.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2015NE00271</t>
+          <t>2015NE00257</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10/2009</t>
+          <t>2/2010</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>31835.61</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2759,19 +2759,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Prestação de serviços de informática em geral, referente ao mês de novembro/2014, relativo ao contrato nº 10/2009 ¿ 5º TA.</t>
+          <t>Prestação de serviços técnicos especializados na área da tecnologia da informação - TI, referente ao mês de novembro/2014, relativo ao contrato nº 002/2010 ¿ 4º TA.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2015NE00257</t>
+          <t>2015NE00271</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/2010</t>
+          <t>10/2009</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>31835.61</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2789,19 +2789,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados na área da tecnologia da informação - TI, referente ao mês de novembro/2014, relativo ao contrato nº 002/2010 ¿ 4º TA.</t>
+          <t>Prestação de serviços de informática em geral, referente ao mês de novembro/2014, relativo ao contrato nº 10/2009 ¿ 5º TA.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2015NE00255</t>
+          <t>2015NE00250</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1/2010</t>
+          <t>10/2009</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>257473.08</v>
+        <v>31835.61</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NE ACIMA DESCRITA DEVIDO A EQUÍVOCO NA FONTE DE RECURSO.</t>
+          <t xml:space="preserve">Prestação de serviços especializados em informática em geral. Serviços de hospedagem com infraestrutura para armazenamento do Sistema de Controle de Material e Patrimônio ¿ AJURI, referente ao mês de </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2015NE00256</t>
+          <t>2015NE00249</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/2010</t>
+          <t>10/2009</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>257473.08</v>
+        <v>31835.61</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados na área de tecnologia da infformação - TI, referente ao mês de novembro/2014, relativo ao Contrato nº 001/2010.</t>
+          <t xml:space="preserve">Prestação de serviços especializados em informática em geral. Serviços de hospedagem com infraestrutura para armazenamento do Sistema de Controle de Material e Patrimônio ¿ AJURI, referente ao mês de </t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024NE0001252</t>
+          <t>2024NE0001251</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convênio de cessão de técnicos, por disposição da PRODAM. para o exercício de funções que visam atuar nos diversos projetos de desenvolvimento, manutenção e suporte técnico dos sistemas da SEFAZ. TC: </t>
+          <t>ANULAÇÃO PARCIAL DA NE ACIMA DESCRITA PARA CORREÇÃO DO REFORÇO 1103, DEVIDO O REFORÇO ESTAR ASSOCIADO AO TERMO ADITIVO ERRADO.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2024NE0001251</t>
+          <t>2024NE0001252</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE ACIMA DESCRITA PARA CORREÇÃO DO REFORÇO 1103, DEVIDO O REFORÇO ESTAR ASSOCIADO AO TERMO ADITIVO ERRADO.</t>
+          <t xml:space="preserve">Convênio de cessão de técnicos, por disposição da PRODAM. para o exercício de funções que visam atuar nos diversos projetos de desenvolvimento, manutenção e suporte técnico dos sistemas da SEFAZ. TC: </t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2016NE01468</t>
+          <t>2016NE01451</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5000</v>
+        <v>453727.43</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3065,14 +3065,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Reforço Orçmentário. Prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI, relativo ao processamento das informações, hospedagem e manutenção de sistemas, a serem pre</t>
+          <t>Cancelamento parcial da NE nº 1119/2016 conforme despacho autorizativo do Secretario Administrativo no Memorando nº 364/2016-GORF.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2016NE01450</t>
+          <t>2016NE01452</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>257813.74</v>
+        <v>5000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cancelamento parcial da NE nº 1047/2016 conforme despacho autorizativo do Secretario Administrativo no Memorando nº 364/2016-GORF.</t>
+          <t>Cancelamento parcial da NE nº 1139/2016 conforme despacho autorizativo do Secretario Administrativo no Memorando nº 364/2016-GORF.</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2016NE01452</t>
+          <t>2016NE01450</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5000</v>
+        <v>257813.74</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3143,14 +3143,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cancelamento parcial da NE nº 1139/2016 conforme despacho autorizativo do Secretario Administrativo no Memorando nº 364/2016-GORF.</t>
+          <t>Cancelamento parcial da NE nº 1047/2016 conforme despacho autorizativo do Secretario Administrativo no Memorando nº 364/2016-GORF.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2016NE01451</t>
+          <t>2016NE01468</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>453727.43</v>
+        <v>5000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cancelamento parcial da NE nº 1119/2016 conforme despacho autorizativo do Secretario Administrativo no Memorando nº 364/2016-GORF.</t>
+          <t>Reforço Orçmentário. Prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI, relativo ao processamento das informações, hospedagem e manutenção de sistemas, a serem pre</t>
         </is>
       </c>
     </row>
@@ -3284,14 +3284,10 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2018NE00319</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2018NE00318</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>16/03/2018</t>
@@ -3307,7 +3303,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
+          <t>Cancelamento da NE acima citada, devido a equívoco no tipo de licitação.</t>
         </is>
       </c>
     </row>
@@ -3344,10 +3340,14 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2018NE00318</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>2018NE00319</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
           <t>16/03/2018</t>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cancelamento da NE acima citada, devido a equívoco no tipo de licitação.</t>
+          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
         </is>
       </c>
     </row>
@@ -3430,10 +3430,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2019NE00659</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>2019NE00657</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>14/06/2019</t>
@@ -3449,21 +3453,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anulação Total da NE acima descrita devido equivoco na data de emissão.</t>
+          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2019NE00657</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2019NE00659</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>14/06/2019</t>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
+          <t>Anulação Total da NE acima descrita devido equivoco na data de emissão.</t>
         </is>
       </c>
     </row>
@@ -3516,21 +3516,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2018NE00703</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2018NE00712</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>528696.76</v>
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3539,28 +3535,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Despesa para prestação de serviços de informática em geral para atender despesa com o Termo de Contrato nº 003/2015-SEFAZ, cujo objeto é a prestação de serviços técnicos especializados na área de Tecn</t>
+          <t>Anulação parcial da NE para ajuste no valor total a ser liquidado.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2018NE00710</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2018NE00706</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>528696.76</v>
+        <v>973265.11</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3569,24 +3561,28 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Despesa para prestação de serviços de informática em geral para atender despesa com o Termo de Contrato nº 003/2015-SEFAZ, cujo objeto é a prestação de serviços técnicos especializados na área de Tecn</t>
+          <t>Cancelamento total da NE para ajuste na natureza de despesa.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2018NE00707</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>2018NE00711</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>P.645/2014</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>528696.76</v>
+        <v>973267.11</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3595,24 +3591,28 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cancelamento total da NE para ajuste na natureza de despesa.</t>
+          <t>Despesa referente à Serviços técnicos especializados na área de tecnologia da informação, com vista a prover suporte à execução das políticas, programas e ações governamentais no que se refere ao proc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2018NE00705</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>2018NE00704</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>P.645/2014</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>973267.11</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3621,28 +3621,24 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE para ajuste no valor da retenção do ISS.</t>
+          <t>Despesa referente à Serviços técnicos especializados na área de tecnologia da informação, com vista a prover suporte à execução das políticas, programas e ações governamentais no que se refere ao proc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2018NE00704</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>P.645/2014</t>
-        </is>
-      </c>
+          <t>2018NE00705</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>973267.11</v>
+        <v>2</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3651,28 +3647,24 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Despesa referente à Serviços técnicos especializados na área de tecnologia da informação, com vista a prover suporte à execução das políticas, programas e ações governamentais no que se refere ao proc</t>
+          <t>Anulação parcial da NE para ajuste no valor da retenção do ISS.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2018NE00711</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>P.645/2014</t>
-        </is>
-      </c>
+          <t>2018NE00707</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>973267.11</v>
+        <v>528696.76</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3681,24 +3673,28 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Despesa referente à Serviços técnicos especializados na área de tecnologia da informação, com vista a prover suporte à execução das políticas, programas e ações governamentais no que se refere ao proc</t>
+          <t>Cancelamento total da NE para ajuste na natureza de despesa.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2018NE00706</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>2018NE00710</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>973265.11</v>
+        <v>528696.76</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3707,24 +3703,28 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cancelamento total da NE para ajuste na natureza de despesa.</t>
+          <t>Despesa para prestação de serviços de informática em geral para atender despesa com o Termo de Contrato nº 003/2015-SEFAZ, cujo objeto é a prestação de serviços técnicos especializados na área de Tecn</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2018NE00712</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>2018NE00703</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>13/07/2018</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>528696.76</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE para ajuste no valor total a ser liquidado.</t>
+          <t>Despesa para prestação de serviços de informática em geral para atender despesa com o Termo de Contrato nº 003/2015-SEFAZ, cujo objeto é a prestação de serviços técnicos especializados na área de Tecn</t>
         </is>
       </c>
     </row>
@@ -3990,12 +3990,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015NE00200</t>
+          <t>2015NE00206</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1/2010</t>
+          <t>2/2010</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>257473.08</v>
+        <v>1121463.19</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL RELATIVO AO CONTRATO Nº 01/2010, REFERENTE AO MÊS 12/2014</t>
+          <t>Prestação de serviços especializados na área de tecnologia da informação, referente ao mês de dezembro/2014, relativo ao contrato nº 002/2010</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2015NE00206</t>
+          <t>2015NE00200</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2/2010</t>
+          <t>1/2010</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1121463.19</v>
+        <v>257473.08</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Prestação de serviços especializados na área de tecnologia da informação, referente ao mês de dezembro/2014, relativo ao contrato nº 002/2010</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL RELATIVO AO CONTRATO Nº 01/2010, REFERENTE AO MÊS 12/2014</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2024NE0000367</t>
+          <t>2024NE0000368</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4207,14 +4207,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Anulação devido a equivoco na descrição da NE.Nº 217</t>
+          <t xml:space="preserve">Convênio de cessão de técnicos, por disposição da PRODAM. para o exercício de funções que visam atuar nos diversos projetos de desenvolvimento, manutenção e suporte técnico dos sistemas da SEFAZ. TC: </t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2024NE0000368</t>
+          <t>2024NE0000367</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convênio de cessão de técnicos, por disposição da PRODAM. para o exercício de funções que visam atuar nos diversos projetos de desenvolvimento, manutenção e suporte técnico dos sistemas da SEFAZ. TC: </t>
+          <t>Anulação devido a equivoco na descrição da NE.Nº 217</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2018NE01102</t>
+          <t>2018NE01103</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>408348.55</v>
+        <v>285919.75</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Anulação do saldo parcial da 2018NE00083.</t>
+          <t>Anulação do saldo parcial da 2018NE00702.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2018NE01103</t>
+          <t>2018NE01102</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>285919.75</v>
+        <v>408348.55</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4393,14 +4393,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Anulação do saldo parcial da 2018NE00702.</t>
+          <t>Anulação do saldo parcial da 2018NE00083.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2018NE00596</t>
+          <t>2018NE00597</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>476107.56</v>
+        <v>0.01</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4419,14 +4419,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Anulação parcial da 2018NE00083 em conformidade ao Memo nº 158/2018 - GORF e autorizado pela SEA/DEPAD.</t>
+          <t>cancelamento por equivoco no valor do empenho.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2018NE00597</t>
+          <t>2018NE00596</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.01</v>
+        <v>476107.56</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4445,24 +4445,28 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>cancelamento por equivoco no valor do empenho.</t>
+          <t>Anulação parcial da 2018NE00083 em conformidade ao Memo nº 158/2018 - GORF e autorizado pela SEA/DEPAD.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2017NE00572</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>2017NE00573</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
           <t>05/05/2017</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>887952.0699999999</v>
+        <v>1331928.09</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4471,7 +4475,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE acima descrita para atender ao 6º TA ao Contrato nº 003/2015..</t>
+          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
         </is>
       </c>
     </row>
@@ -4508,21 +4512,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2017NE00573</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2017NE00572</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>05/05/2017</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1331928.09</v>
+        <v>887952.0699999999</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
+          <t>Anulação parcial da NE acima descrita para atender ao 6º TA ao Contrato nº 003/2015..</t>
         </is>
       </c>
     </row>
@@ -4590,21 +4590,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2015NE00004</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2/2010</t>
-        </is>
-      </c>
+          <t>2015NE00014</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>05/01/2015</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>103959.98</v>
+        <v>2294854.5</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4613,19 +4609,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE AO 4° TA DO CONTRATO N° 02/2010.</t>
+          <t>SALDO REMANESCENTE AO TERMO DE CONVÊNIO Nº 01/2014, CUJO OBJETO É A CESSÃO DE SERVIDORES TÉCNICOS DO QUADRO DE PESSOAL DA PRODAM PARA O EXERCÍCIO DE FUNÇÕES NA SEFAZ/AM, CONFORME PLANO DE TRABALHO.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2015NE00006</t>
+          <t>2015NE00001</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1/2010</t>
+          <t>10/2009</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4634,7 +4630,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>24381.86</v>
+        <v>95506.83</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4643,19 +4639,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE AO 4° TA DO CONTRATO N° 01/2010.</t>
+          <t>SALDO REMANESCENTE AO 5° TA DO CONTRATO N° 010/2009.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2015NE00001</t>
+          <t>2015NE00006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>10/2009</t>
+          <t>1/2010</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4664,7 +4660,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>95506.83</v>
+        <v>24381.86</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4673,24 +4669,28 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE AO 5° TA DO CONTRATO N° 010/2009.</t>
+          <t>SALDO REMANESCENTE AO 4° TA DO CONTRATO N° 01/2010.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2015NE00014</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>2015NE00004</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2/2010</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
           <t>05/01/2015</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2294854.5</v>
+        <v>103959.98</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE AO TERMO DE CONVÊNIO Nº 01/2014, CUJO OBJETO É A CESSÃO DE SERVIDORES TÉCNICOS DO QUADRO DE PESSOAL DA PRODAM PARA O EXERCÍCIO DE FUNÇÕES NA SEFAZ/AM, CONFORME PLANO DE TRABALHO.</t>
+          <t>SALDO REMANESCENTE AO 4° TA DO CONTRATO N° 02/2010.</t>
         </is>
       </c>
     </row>
@@ -4862,21 +4862,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2016NE00091</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2016NE00039</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>986613.41</v>
+        <v>4637951.94</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4885,17 +4881,21 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
+          <t>A Cessão, por disposição, da PRODAM, de técnicos constantes no anexo 1 do plano de trabalho, de acordo com a DIRAF/226-14.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2016NE00090</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>2016NE00041</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C156" t="inlineStr">
         <is>
           <t>04/01/2016</t>
@@ -4911,21 +4911,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>anulação de empenho por motivo de erro no valor global.</t>
+          <t>serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2016NE00041</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2016NE00090</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>04/01/2016</t>
@@ -4941,24 +4937,28 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
+          <t>anulação de empenho por motivo de erro no valor global.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2016NE00039</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+          <t>2016NE00091</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4637951.94</v>
+        <v>986613.41</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>A Cessão, por disposição, da PRODAM, de técnicos constantes no anexo 1 do plano de trabalho, de acordo com a DIRAF/226-14.</t>
+          <t>serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2014NE00137</t>
+          <t>2014NE00138</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/2010</t>
+          <t>1/2010</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>13353598.3</v>
+        <v>3065295.04</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5157,19 +5157,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2010 - Serviços de TI - Uso de Recurso mainframe e Fabrica Software</t>
+          <t>Contrato No. 1/2010 - Serviços Especializados Informatica - Desenvolvimento e Apoio</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2014NE00138</t>
+          <t>2014NE00137</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1/2010</t>
+          <t>2/2010</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3065295.04</v>
+        <v>13353598.3</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Contrato No. 1/2010 - Serviços Especializados Informatica - Desenvolvimento e Apoio</t>
+          <t>Contrato No. 2/2010 - Serviços de TI - Uso de Recurso mainframe e Fabrica Software</t>
         </is>
       </c>
     </row>
@@ -5246,17 +5246,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2024NE0000012</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+          <t>2024NE0000016</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>12/2023</t>
+        </is>
+      </c>
       <c r="C169" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2721136.72</v>
+        <v>31783.32</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5265,7 +5269,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convênio de cessão de técnicos, por disposição da PRODAM. para o exercício de funções que visam atuar nos diversos projetos de desenvolvimento, manutenção e suporte técnico dos sistemas da SEFAZ. TC: </t>
+          <t>Contrato para prestação do serviço de informática, com o desenvolvimento de sistemas de informática compreendendo a análise e desenvolvimento de melhorias ao aplicativo Nota Fiscal Amazonense para a S</t>
         </is>
       </c>
     </row>
@@ -5298,21 +5302,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2024NE0000016</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>12/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000012</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>31783.32</v>
+        <v>2721136.72</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Contrato para prestação do serviço de informática, com o desenvolvimento de sistemas de informática compreendendo a análise e desenvolvimento de melhorias ao aplicativo Nota Fiscal Amazonense para a S</t>
+          <t xml:space="preserve">Convênio de cessão de técnicos, por disposição da PRODAM. para o exercício de funções que visam atuar nos diversos projetos de desenvolvimento, manutenção e suporte técnico dos sistemas da SEFAZ. TC: </t>
         </is>
       </c>
     </row>
@@ -5354,17 +5354,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2020NE00036</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
+          <t>2020NE00032</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C173" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>8564783.5</v>
+        <v>197322.68</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5373,28 +5377,24 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Cessão de servidores da PRODAM para prestar serviços na SEFAZ.</t>
+          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2020NE00032</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2020NE00036</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>197322.68</v>
+        <v>8564783.5</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5403,24 +5403,28 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
+          <t>Cessão de servidores da PRODAM para prestar serviços na SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2019NE00001</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>2019NE00074</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2390426.16</v>
+        <v>295984.02</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5429,28 +5433,24 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cessão de servidores da PRODAM para prestar serviços na SEFAZ.</t>
+          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2019NE00074</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2019NE00001</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>295984.02</v>
+        <v>2390426.16</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5459,24 +5459,28 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Serviços técnicos especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas a serem prestados de forma contínua pa</t>
+          <t>Cessão de servidores da PRODAM para prestar serviços na SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2018NE00083</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
+          <t>2018NE00117</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7905149.3</v>
+        <v>591968.04</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5485,28 +5489,24 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cessão de servidores da PRODAM para prestar serviços na Sefaz/AM.</t>
+          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2018NE00117</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2018NE00083</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>591968.04</v>
+        <v>7905149.3</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5515,19 +5515,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Serviços especializados na área de Tecnologia da Informação - TI, no que se refere ao processamento das informações, hospedagem e manutenção de sistemas, a serem prestados de forma contínua para atend</t>
+          <t>Cessão de servidores da PRODAM para prestar serviços na Sefaz/AM.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2017NE00031</t>
+          <t>2017NE00001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5027712.42</v>
+        <v>129978</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados n área de tecnologia da informação- TI.</t>
+          <t>Contratação de serviços técnicos especializados na área de tecnologia da informação - TI.</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5578,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2017NE00001</t>
+          <t>2017NE00031</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>129978</v>
+        <v>5027712.42</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5601,19 +5601,19 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Contratação de serviços técnicos especializados na área de tecnologia da informação - TI.</t>
+          <t>Prestação de serviços técnicos especializados n área de tecnologia da informação- TI.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2014NE00070</t>
+          <t>2014NE00069</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2/2010</t>
+          <t>1/2010</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>103959.98</v>
+        <v>24381.92</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2010 - Serviços de TI - Uso de Recurso mainframe e Fabrica Software</t>
+          <t>Contrato No. 1/2010 - Serviços Especializados Informatica - Desenvolvimento e Apoio</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2014NE00069</t>
+          <t>2014NE00070</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1/2010</t>
+          <t>2/2010</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>24381.92</v>
+        <v>103959.98</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5691,24 +5691,28 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Contrato No. 1/2010 - Serviços Especializados Informatica - Desenvolvimento e Apoio</t>
+          <t>Contrato No. 2/2010 - Serviços de TI - Uso de Recurso mainframe e Fabrica Software</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2017NE01319</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+          <t>2017NE01304</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>682123.23</v>
+        <v>98661.34</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5717,14 +5721,14 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sessão de servidores da PRODAM para prestar serviços na SEFAZ/AM.</t>
+          <t>Prorrogação do prazo de vigência e supressão, referente a prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2017NE01312</t>
+          <t>2017NE01303</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -5743,14 +5747,14 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Cancelamento da 2017NE01303 para correção do número do processo.</t>
+          <t>Cessão de servidores da PRODAM para prestar serviços na Sefaz/AM.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2017NE01303</t>
+          <t>2017NE01312</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -5769,28 +5773,24 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Cessão de servidores da PRODAM para prestar serviços na Sefaz/AM.</t>
+          <t>Cancelamento da 2017NE01303 para correção do número do processo.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2017NE01304</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2017NE01319</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>98661.34</v>
+        <v>682123.23</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -5799,24 +5799,28 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Prorrogação do prazo de vigência e supressão, referente a prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI.</t>
+          <t>Sessão de servidores da PRODAM para prestar serviços na SEFAZ/AM.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2016NE01401</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
+          <t>2016NE00088</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>21/2016</t>
+        </is>
+      </c>
       <c r="C189" t="inlineStr">
         <is>
           <t>01/11/2016</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>772991.99</v>
+        <v>64989</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5825,14 +5829,14 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cancelamento da NE acima descrita para ajuste na descrição.</t>
+          <t>Termo de Contrato nº 021/2016 cujo objeto é a prestação de serviços técnicos especializados na área de Tecnologia da Informação TI Obs.: Reforço da NE 2016NE00053 para atender o mês novembro/2016</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2016NE01391</t>
+          <t>2016NE01402</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -5842,7 +5846,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>100000</v>
+        <v>772991.99</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5851,7 +5855,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Reforço Orçmentário. Prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI, relativo ao processamento das informações, hospedagem e manutenção de sistemas, a serem pre</t>
+          <t>2º Termo Aditivo ao Convênio nº 05/2015, relativo a cessão, por disposição, da PRODAM, de técnicos constantes no anexo 1 do plano de trabalho, de acordo com a DP 842/15.</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5888,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2016NE01402</t>
+          <t>2016NE01391</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -5894,7 +5898,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>772991.99</v>
+        <v>100000</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -5903,28 +5907,24 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Convênio nº 05/2015, relativo a cessão, por disposição, da PRODAM, de técnicos constantes no anexo 1 do plano de trabalho, de acordo com a DP 842/15.</t>
+          <t>Reforço Orçmentário. Prestação de serviços técnicos especializados na área de Tecnologia da Informação - TI, relativo ao processamento das informações, hospedagem e manutenção de sistemas, a serem pre</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2016NE00088</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>21/2016</t>
-        </is>
-      </c>
+          <t>2016NE01401</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
           <t>01/11/2016</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>64989</v>
+        <v>772991.99</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 021/2016 cujo objeto é a prestação de serviços técnicos especializados na área de Tecnologia da Informação TI Obs.: Reforço da NE 2016NE00053 para atender o mês novembro/2016</t>
+          <t>Cancelamento da NE acima descrita para ajuste na descrição.</t>
         </is>
       </c>
     </row>
@@ -6026,12 +6026,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2016NE00939</t>
+          <t>2016NE00053</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>826584.71</v>
+        <v>220759.24</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6049,14 +6049,14 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestação de serviços técnicos especializados na área de tecnologia da informação, para prover suporte à execução das políticas, programas e ações governamentais no que se refere ao processamento das </t>
+          <t>Serviços de BI</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2016NE00940</t>
+          <t>2016NE00942</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -6075,21 +6075,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Cancelamento da NE acima descrita devido a equívoco na referência da licitação.</t>
+          <t>Cancelamento da NE acima para correção do número do processo.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2016NE00943</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2016NE00903</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
           <t>01/07/2016</t>
@@ -6105,14 +6101,14 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestação de serviços técnicos especializados na área de tecnologia da informação, para prover suporte à execução das políticas, programas e ações governamentais no que se refere ao processamento das </t>
+          <t>Emissão indevida.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2016NE00941</t>
+          <t>2016NE00901</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6135,14 +6131,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestação de serviços técnicos especializados na área de tecnologia da informação, para prover suporte à execução das políticas, programas e ações governamentais no que se refere ao processamento das </t>
+          <t>3º TA ao Contrato nº 003/2015, cujo objeto é a redução do valor mensal do contrato.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2016NE00901</t>
+          <t>2016NE00941</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6165,17 +6161,21 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>3º TA ao Contrato nº 003/2015, cujo objeto é a redução do valor mensal do contrato.</t>
+          <t xml:space="preserve">Prestação de serviços técnicos especializados na área de tecnologia da informação, para prover suporte à execução das políticas, programas e ações governamentais no que se refere ao processamento das </t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2016NE00903</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>2016NE00943</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
           <t>01/07/2016</t>
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Emissão indevida.</t>
+          <t xml:space="preserve">Prestação de serviços técnicos especializados na área de tecnologia da informação, para prover suporte à execução das políticas, programas e ações governamentais no que se refere ao processamento das </t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2016NE00942</t>
+          <t>2016NE00940</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -6217,19 +6217,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Cancelamento da NE acima para correção do número do processo.</t>
+          <t>Cancelamento da NE acima descrita devido a equívoco na referência da licitação.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2016NE00053</t>
+          <t>2016NE00939</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>220759.24</v>
+        <v>826584.71</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6247,28 +6247,24 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Serviços de BI</t>
+          <t xml:space="preserve">Prestação de serviços técnicos especializados na área de tecnologia da informação, para prover suporte à execução das políticas, programas e ações governamentais no que se refere ao processamento das </t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2015NE00595</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>3/2015</t>
-        </is>
-      </c>
+          <t>2015NE00592</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
           <t>01/04/2015</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>10446494.94</v>
+        <v>5354660.5</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6277,7 +6273,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - Contrato 003/2015 - Serviços de TI Abril/15 a Dezembro/15 R$ 1.160.721,66 (NE 595 de 01/04/15 no valor de R$ 10.446.494,94</t>
+          <t>Saldo remanescente ao Termo de Convênio nº 02/2014 de cessão de servidores a ser firmado, celebrado entre o Estado do Amazonas, por intermédio da SEFAZ e a PRODAM. OBJETO: Cessão, por disposição, da P</t>
         </is>
       </c>
     </row>
@@ -6314,17 +6310,21 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2015NE00592</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
+          <t>2015NE00595</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>3/2015</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
           <t>01/04/2015</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5354660.5</v>
+        <v>10446494.94</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Saldo remanescente ao Termo de Convênio nº 02/2014 de cessão de servidores a ser firmado, celebrado entre o Estado do Amazonas, por intermédio da SEFAZ e a PRODAM. OBJETO: Cessão, por disposição, da P</t>
+          <t>Cobertura Financeira 2015 - Contrato 003/2015 - Serviços de TI Abril/15 a Dezembro/15 R$ 1.160.721,66 (NE 595 de 01/04/15 no valor de R$ 10.446.494,94</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SEFAZ/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEFAZ/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-10-31</t>
         </is>
       </c>
     </row>
